--- a/docs/downloads/03092026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/03092026Tduh Developer Project Sales Status 13.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:BG18"/>
+  <dimension ref="A2:BJ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -550,6 +550,9 @@
     <col width="9" customWidth="1" min="57" max="57"/>
     <col width="9" customWidth="1" min="58" max="58"/>
     <col width="9" customWidth="1" min="59" max="59"/>
+    <col width="9" customWidth="1" min="60" max="60"/>
+    <col width="9" customWidth="1" min="61" max="61"/>
+    <col width="9" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -616,8 +619,11 @@
       <c r="BB3" s="3" t="n">
         <v>46255</v>
       </c>
-      <c r="BE3" s="4" t="n">
+      <c r="BE3" s="3" t="n">
         <v>46262</v>
+      </c>
+      <c r="BH3" s="4" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -904,17 +910,32 @@
           <t>%</t>
         </is>
       </c>
-      <c r="BE4" s="6" t="inlineStr">
+      <c r="BE4" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW SALES </t>
         </is>
       </c>
-      <c r="BF4" s="6" t="inlineStr">
+      <c r="BF4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="BG4" s="6" t="inlineStr">
+      <c r="BG4" s="5" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="BH4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEW SALES </t>
+        </is>
+      </c>
+      <c r="BI4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="BJ4" s="6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
@@ -1008,15 +1029,26 @@
         <f>BC5/$D$5</f>
         <v/>
       </c>
-      <c r="BE5" s="12">
+      <c r="BE5" s="10">
         <f>BF5-BC5</f>
         <v/>
       </c>
-      <c r="BF5" s="12" t="n">
+      <c r="BF5" s="10" t="n">
         <v>188</v>
       </c>
-      <c r="BG5" s="13">
+      <c r="BG5" s="11">
         <f>BF5/$D$5</f>
+        <v/>
+      </c>
+      <c r="BH5" s="12">
+        <f>BI5-BF5</f>
+        <v/>
+      </c>
+      <c r="BI5" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="BJ5" s="13">
+        <f>BI5/$D$5</f>
         <v/>
       </c>
     </row>
@@ -1228,15 +1260,26 @@
         <f>BC6/$D$6</f>
         <v/>
       </c>
-      <c r="BE6" s="12">
+      <c r="BE6" s="10">
         <f>BF6-BC6</f>
         <v/>
       </c>
-      <c r="BF6" s="12" t="n">
+      <c r="BF6" s="10" t="n">
         <v>355</v>
       </c>
-      <c r="BG6" s="13">
+      <c r="BG6" s="11">
         <f>BF6/$D$6</f>
+        <v/>
+      </c>
+      <c r="BH6" s="12">
+        <f>BI6-BF6</f>
+        <v/>
+      </c>
+      <c r="BI6" s="12" t="n">
+        <v>365</v>
+      </c>
+      <c r="BJ6" s="13">
+        <f>BI6/$D$6</f>
         <v/>
       </c>
     </row>
@@ -1449,15 +1492,26 @@
         <f>BC7/$D$7</f>
         <v/>
       </c>
-      <c r="BE7" s="12">
+      <c r="BE7" s="10">
         <f>BF7-BC7</f>
         <v/>
       </c>
-      <c r="BF7" s="12" t="n">
+      <c r="BF7" s="10" t="n">
         <v>128</v>
       </c>
-      <c r="BG7" s="13">
+      <c r="BG7" s="11">
         <f>BF7/$D$7</f>
+        <v/>
+      </c>
+      <c r="BH7" s="12">
+        <f>BI7-BF7</f>
+        <v/>
+      </c>
+      <c r="BI7" s="12" t="n">
+        <v>131</v>
+      </c>
+      <c r="BJ7" s="13">
+        <f>BI7/$D$7</f>
         <v/>
       </c>
     </row>
@@ -1669,15 +1723,26 @@
         <f>BC8/$D$8</f>
         <v/>
       </c>
-      <c r="BE8" s="12">
+      <c r="BE8" s="10">
         <f>BF8-BC8</f>
         <v/>
       </c>
-      <c r="BF8" s="12" t="n">
+      <c r="BF8" s="10" t="n">
         <v>1009</v>
       </c>
-      <c r="BG8" s="13">
+      <c r="BG8" s="11">
         <f>BF8/$D$8</f>
+        <v/>
+      </c>
+      <c r="BH8" s="12">
+        <f>BI8-BF8</f>
+        <v/>
+      </c>
+      <c r="BI8" s="12" t="n">
+        <v>1013</v>
+      </c>
+      <c r="BJ8" s="13">
+        <f>BI8/$D$8</f>
         <v/>
       </c>
     </row>
@@ -1890,15 +1955,26 @@
         <f>BC9/$D$9</f>
         <v/>
       </c>
-      <c r="BE9" s="12">
+      <c r="BE9" s="10">
         <f>BF9-BC9</f>
         <v/>
       </c>
-      <c r="BF9" s="12" t="n">
+      <c r="BF9" s="10" t="n">
         <v>1126</v>
       </c>
-      <c r="BG9" s="13">
+      <c r="BG9" s="11">
         <f>BF9/$D$9</f>
+        <v/>
+      </c>
+      <c r="BH9" s="12">
+        <f>BI9-BF9</f>
+        <v/>
+      </c>
+      <c r="BI9" s="12" t="n">
+        <v>1128</v>
+      </c>
+      <c r="BJ9" s="13">
+        <f>BI9/$D$9</f>
         <v/>
       </c>
     </row>
@@ -2111,15 +2187,26 @@
         <f>BC10/$D$10</f>
         <v/>
       </c>
-      <c r="BE10" s="12">
+      <c r="BE10" s="10">
         <f>BF10-BC10</f>
         <v/>
       </c>
-      <c r="BF10" s="12" t="n">
+      <c r="BF10" s="10" t="n">
         <v>519</v>
       </c>
-      <c r="BG10" s="13">
+      <c r="BG10" s="11">
         <f>BF10/$D$10</f>
+        <v/>
+      </c>
+      <c r="BH10" s="12">
+        <f>BI10-BF10</f>
+        <v/>
+      </c>
+      <c r="BI10" s="12" t="n">
+        <v>521</v>
+      </c>
+      <c r="BJ10" s="13">
+        <f>BI10/$D$10</f>
         <v/>
       </c>
     </row>
@@ -2331,15 +2418,26 @@
         <f>BC11/$D$11</f>
         <v/>
       </c>
-      <c r="BE11" s="12">
+      <c r="BE11" s="10">
         <f>BF11-BC11</f>
         <v/>
       </c>
-      <c r="BF11" s="12" t="n">
+      <c r="BF11" s="10" t="n">
         <v>467</v>
       </c>
-      <c r="BG11" s="13">
+      <c r="BG11" s="11">
         <f>BF11/$D$11</f>
+        <v/>
+      </c>
+      <c r="BH11" s="12">
+        <f>BI11-BF11</f>
+        <v/>
+      </c>
+      <c r="BI11" s="12" t="n">
+        <v>469</v>
+      </c>
+      <c r="BJ11" s="13">
+        <f>BI11/$D$11</f>
         <v/>
       </c>
     </row>
@@ -2551,15 +2649,26 @@
         <f>BC12/$D$12</f>
         <v/>
       </c>
-      <c r="BE12" s="12">
+      <c r="BE12" s="10">
         <f>BF12-BC12</f>
         <v/>
       </c>
-      <c r="BF12" s="12" t="n">
+      <c r="BF12" s="10" t="n">
         <v>237</v>
       </c>
-      <c r="BG12" s="13">
+      <c r="BG12" s="11">
         <f>BF12/$D$12</f>
+        <v/>
+      </c>
+      <c r="BH12" s="12">
+        <f>BI12-BF12</f>
+        <v/>
+      </c>
+      <c r="BI12" s="12" t="n">
+        <v>238</v>
+      </c>
+      <c r="BJ12" s="13">
+        <f>BI12/$D$12</f>
         <v/>
       </c>
     </row>
@@ -2772,15 +2881,26 @@
         <f>BC13/$D$13</f>
         <v/>
       </c>
-      <c r="BE13" s="12">
+      <c r="BE13" s="10">
         <f>BF13-BC13</f>
         <v/>
       </c>
-      <c r="BF13" s="12" t="n">
+      <c r="BF13" s="10" t="n">
         <v>647</v>
       </c>
-      <c r="BG13" s="13">
+      <c r="BG13" s="11">
         <f>BF13/$D$13</f>
+        <v/>
+      </c>
+      <c r="BH13" s="12">
+        <f>BI13-BF13</f>
+        <v/>
+      </c>
+      <c r="BI13" s="12" t="n">
+        <v>653</v>
+      </c>
+      <c r="BJ13" s="13">
+        <f>BI13/$D$13</f>
         <v/>
       </c>
     </row>
@@ -2992,15 +3112,26 @@
         <f>BC14/$D$14</f>
         <v/>
       </c>
-      <c r="BE14" s="12">
+      <c r="BE14" s="10">
         <f>BF14-BC14</f>
         <v/>
       </c>
-      <c r="BF14" s="12" t="n">
+      <c r="BF14" s="10" t="n">
         <v>1157</v>
       </c>
-      <c r="BG14" s="13">
+      <c r="BG14" s="11">
         <f>BF14/$D$14</f>
+        <v/>
+      </c>
+      <c r="BH14" s="12">
+        <f>BI14-BF14</f>
+        <v/>
+      </c>
+      <c r="BI14" s="12" t="n">
+        <v>1163</v>
+      </c>
+      <c r="BJ14" s="13">
+        <f>BI14/$D$14</f>
         <v/>
       </c>
     </row>
@@ -3212,15 +3343,26 @@
         <f>BC15/$D$15</f>
         <v/>
       </c>
-      <c r="BE15" s="12">
+      <c r="BE15" s="10">
         <f>BF15-BC15</f>
         <v/>
       </c>
-      <c r="BF15" s="12" t="n">
+      <c r="BF15" s="10" t="n">
         <v>134</v>
       </c>
-      <c r="BG15" s="13">
+      <c r="BG15" s="11">
         <f>BF15/$D$15</f>
+        <v/>
+      </c>
+      <c r="BH15" s="12">
+        <f>BI15-BF15</f>
+        <v/>
+      </c>
+      <c r="BI15" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="BJ15" s="13">
+        <f>BI15/$D$15</f>
         <v/>
       </c>
     </row>
@@ -3368,15 +3510,26 @@
         <f>BC16/$D$16</f>
         <v/>
       </c>
-      <c r="BE16" s="12">
+      <c r="BE16" s="10">
         <f>BF16-BC16</f>
         <v/>
       </c>
-      <c r="BF16" s="12" t="n">
+      <c r="BF16" s="10" t="n">
         <v>659</v>
       </c>
-      <c r="BG16" s="13">
+      <c r="BG16" s="11">
         <f>BF16/$D$16</f>
+        <v/>
+      </c>
+      <c r="BH16" s="12">
+        <f>BI16-BF16</f>
+        <v/>
+      </c>
+      <c r="BI16" s="12" t="n">
+        <v>659</v>
+      </c>
+      <c r="BJ16" s="13">
+        <f>BI16/$D$16</f>
         <v/>
       </c>
     </row>
@@ -3449,9 +3602,12 @@
       <c r="BB17" s="10" t="n"/>
       <c r="BC17" s="10" t="n"/>
       <c r="BD17" s="11" t="n"/>
-      <c r="BE17" s="12" t="n"/>
-      <c r="BF17" s="12" t="n"/>
-      <c r="BG17" s="13" t="n"/>
+      <c r="BE17" s="10" t="n"/>
+      <c r="BF17" s="10" t="n"/>
+      <c r="BG17" s="11" t="n"/>
+      <c r="BH17" s="12" t="n"/>
+      <c r="BI17" s="12" t="n"/>
+      <c r="BJ17" s="13" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -3541,38 +3697,50 @@
         <f>BC18/$D$18</f>
         <v/>
       </c>
-      <c r="BE18" s="12">
+      <c r="BE18" s="10">
         <f>BF18-BC18</f>
         <v/>
       </c>
-      <c r="BF18" s="12" t="n">
+      <c r="BF18" s="10" t="n">
         <v>260</v>
       </c>
-      <c r="BG18" s="13">
+      <c r="BG18" s="11">
         <f>BF18/$D$18</f>
+        <v/>
+      </c>
+      <c r="BH18" s="12">
+        <f>BI18-BF18</f>
+        <v/>
+      </c>
+      <c r="BI18" s="12" t="n">
+        <v>303</v>
+      </c>
+      <c r="BJ18" s="13">
+        <f>BI18/$D$18</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="AY3:BA3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:W3"/>
-    <mergeCell ref="BE3:BG3"/>
-    <mergeCell ref="AD3:AF3"/>
-    <mergeCell ref="AP3:AR3"/>
+  <mergeCells count="19">
     <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="AJ3:AL3"/>
     <mergeCell ref="I3:K3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="AG3:AI3"/>
+    <mergeCell ref="AA3:AC3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="AM3:AO3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AD3:AF3"/>
+    <mergeCell ref="AY3:BA3"/>
+    <mergeCell ref="BE3:BG3"/>
+    <mergeCell ref="AP3:AR3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="BB3:BD3"/>
     <mergeCell ref="AV3:AX3"/>
     <mergeCell ref="L3:N3"/>
-    <mergeCell ref="AA3:AC3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="AM3:AO3"/>
-    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="BH3:BJ3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
